--- a/data/test_Predictions.xlsx
+++ b/data/test_Predictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvesgreatti/github/Variant-Effects/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA35105-B6D9-6240-8170-2DB3A4EAB4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E97199-D5E5-2349-BC2A-93B3E4F8D129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="9820" windowWidth="35840" windowHeight="10880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="580" yWindow="9780" windowWidth="35840" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="156">
   <si>
     <t>#CHROM</t>
   </si>
@@ -254,6 +254,240 @@
   </si>
   <si>
     <t>Transcript</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>TSC1</t>
+  </si>
+  <si>
+    <t>9:132923492T&gt;C:TSC1</t>
+  </si>
+  <si>
+    <t>p.M71V</t>
+  </si>
+  <si>
+    <t>Q92574</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>TTGCTGCTGC</t>
+  </si>
+  <si>
+    <t>RET</t>
+  </si>
+  <si>
+    <t>10:43077301T&gt;TTGCTGCTGC:RET</t>
+  </si>
+  <si>
+    <t>p.L19_P20insLLL</t>
+  </si>
+  <si>
+    <t>P07949</t>
+  </si>
+  <si>
+    <t>GGCGGCGGCGGCC</t>
+  </si>
+  <si>
+    <t>PTEN</t>
+  </si>
+  <si>
+    <t>10:87863973G&gt;GGCGGCGGCGGCC:PTEN</t>
+  </si>
+  <si>
+    <t>p.A17_P18insAAAA</t>
+  </si>
+  <si>
+    <t>P60484</t>
+  </si>
+  <si>
+    <t>GGCGGCGGCC</t>
+  </si>
+  <si>
+    <t>10:87863976G&gt;GGCGGCGGCC:PTEN</t>
+  </si>
+  <si>
+    <t>p.A17_P18insAAA</t>
+  </si>
+  <si>
+    <t>GGCGGCC</t>
+  </si>
+  <si>
+    <t>10:87863979G&gt;GGCGGCC:PTEN</t>
+  </si>
+  <si>
+    <t>p.A17_P18insAA</t>
+  </si>
+  <si>
+    <t>GGCGGCCGCGGCGGCTGCA</t>
+  </si>
+  <si>
+    <t>10:87863979G&gt;GGCGGCCGCGGCGGCTGCA:PTEN</t>
+  </si>
+  <si>
+    <t>p.A17_P18insAAAAAA</t>
+  </si>
+  <si>
+    <t>CGCGGCGGCT</t>
+  </si>
+  <si>
+    <t>10:87863985C&gt;CGCGGCGGCT:PTEN</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>AGGC</t>
+  </si>
+  <si>
+    <t>WT1</t>
+  </si>
+  <si>
+    <t>11:32434938A&gt;AGGC:WT1</t>
+  </si>
+  <si>
+    <t>p.P141_H142insP</t>
+  </si>
+  <si>
+    <t>P19544</t>
+  </si>
+  <si>
+    <t>GGCCTCGGCC</t>
+  </si>
+  <si>
+    <t>MEN1</t>
+  </si>
+  <si>
+    <t>11:64804766G&gt;GGCCTCGGCC:MEN1</t>
+  </si>
+  <si>
+    <t>p.A412_E413insAEA</t>
+  </si>
+  <si>
+    <t>O00255</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>GCCGCCC</t>
+  </si>
+  <si>
+    <t>RB1</t>
+  </si>
+  <si>
+    <t>13:48303987G&gt;GCCGCCC:RB1</t>
+  </si>
+  <si>
+    <t>p.P29_E30insPP</t>
+  </si>
+  <si>
+    <t>P06400</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>TSC2</t>
+  </si>
+  <si>
+    <t>16:2050409A&gt;G:TSC2</t>
+  </si>
+  <si>
+    <t>P49815</t>
+  </si>
+  <si>
+    <t>CCAGCGGGTAGGGAATATGGGGCTCCCT</t>
+  </si>
+  <si>
+    <t>16:2088319C&gt;CCAGCGGGTAGGGAATATGGGGCTCCCT:TSC2</t>
+  </si>
+  <si>
+    <t>p.R1638_I1639insVGNMGLPQR</t>
+  </si>
+  <si>
+    <t>PALB2</t>
+  </si>
+  <si>
+    <t>16:23641156A&gt;G:PALB2</t>
+  </si>
+  <si>
+    <t>Q86YC2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>TP53</t>
+  </si>
+  <si>
+    <t>17:7675134T&gt;C:TP53</t>
+  </si>
+  <si>
+    <t>p.M28V</t>
+  </si>
+  <si>
+    <t>P04637</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>BRCA1</t>
+  </si>
+  <si>
+    <t>17:43057062T&gt;TG:BRCA1</t>
+  </si>
+  <si>
+    <t>p.Q66Pfs</t>
+  </si>
+  <si>
+    <t>P38398</t>
+  </si>
+  <si>
+    <t>GCCACATGGCT</t>
+  </si>
+  <si>
+    <t>17:43094706G&gt;GCCACATGGCT:BRCA1</t>
+  </si>
+  <si>
+    <t>p.T229Afs</t>
+  </si>
+  <si>
+    <t>ENST00000545250.5</t>
+  </si>
+  <si>
+    <t>ENST00000340058.6</t>
+  </si>
+  <si>
+    <t>ENST00000693560.1</t>
+  </si>
+  <si>
+    <t>ENST00000332351.9</t>
+  </si>
+  <si>
+    <t>ENST00000377316.6</t>
+  </si>
+  <si>
+    <t>ENST00000267163.6</t>
+  </si>
+  <si>
+    <t>ENST00000382538.10</t>
+  </si>
+  <si>
+    <t>ENST00000261584.9</t>
+  </si>
+  <si>
+    <t>ENST00000504290.5</t>
+  </si>
+  <si>
+    <t>ENST00000586385.5</t>
+  </si>
+  <si>
+    <t>ENST00000634433.1</t>
   </si>
 </sst>
 </file>
@@ -624,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1234,6 +1468,569 @@
         <v>66</v>
       </c>
     </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18">
+        <v>132923492</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19">
+        <v>43077301</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>87</v>
+      </c>
+      <c r="K19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20">
+        <v>87863973</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21">
+        <v>87863976</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22">
+        <v>87863979</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23">
+        <v>87863979</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24">
+        <v>87863985</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25">
+        <v>32434938</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26">
+        <v>64804766</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27">
+        <v>48303987</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="K27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28">
+        <v>2050409</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29">
+        <v>2088319</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30">
+        <v>23641156</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31">
+        <v>7675134</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32">
+        <v>43057062</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32">
+        <v>5</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33">
+        <v>43094706</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>144</v>
+      </c>
+      <c r="K33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J35" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
